--- a/output/pdf_financials_xlsx/ELVA.xlsx
+++ b/output/pdf_financials_xlsx/ELVA.xlsx
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.995</v>
+        <v>-1.995</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.872</v>
+        <v>-3.872</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.446</v>
+        <v>-3.446</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-8.791</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.995</v>
+        <v>-1.995</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.872</v>
+        <v>-3.872</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.446</v>
+        <v>-3.446</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-8.791</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.995</v>
+        <v>-1.995</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.872</v>
+        <v>-3.872</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-4.561</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.446</v>
+        <v>-3.446</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-8.791</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>66.5</v>
+        <v>-66.5</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>77.44</v>
+        <v>-77.44</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>68.92</v>
+        <v>-68.92</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>79.825</v>
+        <v>-79.825</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.995</v>
+        <v>-1.995</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.872</v>
+        <v>-3.872</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.446</v>
+        <v>-3.446</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-8.791</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.995</v>
+        <v>-1.995</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.872</v>
+        <v>-3.872</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.446</v>
+        <v>-3.446</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-8.791</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>19.43686671862822</v>
+        <v>-19.43686671862822</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>39.29368784250051</v>
+        <v>-39.29368784250051</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46.54240950837385</v>
+        <v>-46.54240950837385</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.27209077740222</v>
+        <v>-19.27209077740222</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-45.00127975428718</v>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>19.43686671862822</v>
+        <v>-19.43686671862822</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>39.29368784250051</v>
+        <v>-39.29368784250051</v>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46.54240950837385</v>
+        <v>-46.54240950837385</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>19.27209077740222</v>
+        <v>-19.27209077740222</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>-45.00127975428718</v>
@@ -43413,10 +43413,10 @@
         </is>
       </c>
       <c r="F372" s="5" t="n">
-        <v>1.995</v>
+        <v>-1.995</v>
       </c>
       <c r="G372" s="5" t="n">
-        <v>3.872</v>
+        <v>-3.872</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
@@ -43424,10 +43424,10 @@
         </is>
       </c>
       <c r="I372" s="5" t="n">
-        <v>3.446</v>
+        <v>-3.446</v>
       </c>
       <c r="J372" s="5" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ELVA.xlsx
+++ b/output/pdf_financials_xlsx/ELVA.xlsx
@@ -1047,40 +1047,40 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.631</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.573</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.049</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.166</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.256</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.546</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.887</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.152</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2012,40 +2012,40 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.446</v>
+        <v>-2.815</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.193</v>
+        <v>-2.62</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-8.791</v>
+        <v>-8.601000000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-21.174</v>
+        <v>-21.125</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-22.657</v>
+        <v>-22.677</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.837</v>
+        <v>-2.872</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.112</v>
+        <v>1.278</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-7.534</v>
+        <v>-7.278</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-6.547</v>
+        <v>-7.093</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.158</v>
+        <v>-3.045</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.485</v>
+        <v>-1.333</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.31</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
@@ -2130,40 +2130,40 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.446</v>
+        <v>-2.815</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.193</v>
+        <v>-2.62</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8.791</v>
+        <v>-8.601000000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-21.174</v>
+        <v>-21.125</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-22.657</v>
+        <v>-22.677</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.837</v>
+        <v>-2.872</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.112</v>
+        <v>1.278</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-7.534</v>
+        <v>-7.278</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.547</v>
+        <v>-7.093</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.251</v>
+        <v>-2.138</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.276</v>
+        <v>-0.124</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.837</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="30">
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-46.54240950837385</v>
+        <v>-38.01998919502972</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-19.27209077740222</v>
+        <v>-15.81361661033317</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-45.00127975428718</v>
+        <v>-44.02866649603276</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-930.7252747252746</v>
+        <v>-928.5714285714287</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-402.219066216936</v>
+        <v>-402.5741168116457</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-58.00449805765692</v>
+        <v>-58.72009813943979</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7.655765920826162</v>
+        <v>8.798623063683305</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-65.03798342541437</v>
+        <v>-62.82803867403315</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-33.02729153004086</v>
+        <v>-35.78166775967311</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-10.55161943319838</v>
+        <v>-18.03306342780027</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-2.016217400832785</v>
+        <v>-0.9058368032727008</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>14.38640973630832</v>
+        <v>11.54665314401623</v>
       </c>
     </row>
     <row r="31">
@@ -40840,7 +40840,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -45740,7 +45740,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -50342,7 +50342,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">

--- a/output/pdf_financials_xlsx/ELVA.xlsx
+++ b/output/pdf_financials_xlsx/ELVA.xlsx
@@ -602,13 +602,13 @@
         <v>19.823</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>11.856</v>
+        <v>44.059</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>13.689</v>
+        <v>44.615</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>19.72</v>
+        <v>63.826</v>
       </c>
     </row>
     <row r="5">
@@ -661,13 +661,13 @@
         <v>14.847</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>32.203</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
+        <v>30.926</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>44.106</v>
       </c>
     </row>
     <row r="6">
@@ -2216,13 +2216,13 @@
         <v>-35.78166775967311</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-18.03306342780027</v>
+        <v>-4.852584035043918</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.9058368032727008</v>
+        <v>-0.2779334304606074</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11.54665314401623</v>
+        <v>3.567511672359227</v>
       </c>
     </row>
     <row r="31">
@@ -2334,13 +2334,13 @@
         <v>-33.02729153004086</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>-12.4746963562753</v>
+        <v>-3.356862389069203</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-10.84812623274162</v>
+        <v>-3.328476969629048</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>17.05375253549696</v>
+        <v>5.2690126280826</v>
       </c>
     </row>
     <row r="33">
@@ -3167,13 +3167,13 @@
         <v>4.477</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>0</v>
+        <v>8.266</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>0</v>
+        <v>9.698</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>0</v>
+        <v>12.451</v>
       </c>
     </row>
     <row r="48">
@@ -3226,13 +3226,13 @@
         <v>4.269</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>14.263</v>
+        <v>5.997</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>17.345</v>
+        <v>7.647</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>19.124</v>
+        <v>6.673</v>
       </c>
     </row>
     <row r="49">
@@ -4332,13 +4332,13 @@
         <v>0.391</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="67">
@@ -5674,13 +5674,13 @@
         <v>103.305</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>115.041</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>116.408</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>134.866</v>
       </c>
     </row>
     <row r="89">
@@ -7712,13 +7712,13 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.707</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.735</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="125">
@@ -7769,13 +7769,13 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.707</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.735</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="126">
@@ -9002,7 +9002,11 @@
           <t>Inventories Note 6</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9094,7 +9098,11 @@
           <t>Prepaid expenses Note 7</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10872,7 +10880,11 @@
           <t>Other payables Note 22</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11048,7 +11060,11 @@
           <t>Share capital Note 14</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11852,7 +11868,11 @@
           <t>Prepaid expenses Note 8</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -12894,7 +12914,11 @@
           <t>Other payables Note 23</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12984,7 +13008,11 @@
           <t>Share capital Note 15</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -27372,7 +27400,11 @@
           <t>Lease payments Note 13</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -30292,7 +30324,11 @@
           <t>Lease payments Note 14</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -39700,7 +39736,11 @@
           <t>Revenue Note 21</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -42926,7 +42966,11 @@
           <t>Revenue Note 22</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
